--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/75.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/75.xlsx
@@ -426,13 +426,13 @@
         <v>-4.183630644014809</v>
       </c>
       <c r="E2">
-        <v>-6.76064160820937</v>
+        <v>-8.199924533194727</v>
       </c>
       <c r="F2">
-        <v>-3.065170771293392</v>
+        <v>-3.355990685598631</v>
       </c>
       <c r="G2">
-        <v>-8.41769792521711</v>
+        <v>-8.772256621274728</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.693324201755736</v>
       </c>
       <c r="E3">
-        <v>-6.290743125706943</v>
+        <v>-8.331477501908671</v>
       </c>
       <c r="F3">
-        <v>-2.833457356280106</v>
+        <v>-3.451836107572146</v>
       </c>
       <c r="G3">
-        <v>-8.055991010469025</v>
+        <v>-8.549618849406066</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.10249937191119</v>
       </c>
       <c r="E4">
-        <v>-7.143455555652791</v>
+        <v>-9.572295070525771</v>
       </c>
       <c r="F4">
-        <v>-3.117592345644753</v>
+        <v>-3.461438542505397</v>
       </c>
       <c r="G4">
-        <v>-7.448713543363938</v>
+        <v>-7.870249586534271</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.52724340000081</v>
       </c>
       <c r="E5">
-        <v>-6.552794147458326</v>
+        <v>-10.11527761271121</v>
       </c>
       <c r="F5">
-        <v>-2.303760305662171</v>
+        <v>-3.295687195409633</v>
       </c>
       <c r="G5">
-        <v>-8.089364158577226</v>
+        <v>-7.601191470463318</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.003023118060071</v>
       </c>
       <c r="E6">
-        <v>-8.581696024595615</v>
+        <v>-11.35269370125327</v>
       </c>
       <c r="F6">
-        <v>-2.277066166106957</v>
+        <v>-3.224402866929124</v>
       </c>
       <c r="G6">
-        <v>-7.420768133260661</v>
+        <v>-7.007889319154459</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.574746930400929</v>
       </c>
       <c r="E7">
-        <v>-10.85494793681787</v>
+        <v>-12.32420458793451</v>
       </c>
       <c r="F7">
-        <v>-2.288168774406679</v>
+        <v>-2.800587737737022</v>
       </c>
       <c r="G7">
-        <v>-7.436623185162492</v>
+        <v>-6.780109685813598</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.245694069608932</v>
       </c>
       <c r="E8">
-        <v>-9.653785229930232</v>
+        <v>-12.46575433630732</v>
       </c>
       <c r="F8">
-        <v>-2.719213065923012</v>
+        <v>-3.427291581427196</v>
       </c>
       <c r="G8">
-        <v>-7.189751176626819</v>
+        <v>-5.878744894242554</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.009604354257852</v>
       </c>
       <c r="E9">
-        <v>-10.81384360433604</v>
+        <v>-13.51912501820093</v>
       </c>
       <c r="F9">
-        <v>-2.655975498393298</v>
+        <v>-3.017950515864209</v>
       </c>
       <c r="G9">
-        <v>-6.380979052724199</v>
+        <v>-5.445604091364722</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.8374437659047796</v>
       </c>
       <c r="E10">
-        <v>-11.89394435431625</v>
+        <v>-14.16120318259678</v>
       </c>
       <c r="F10">
-        <v>-2.541889426210139</v>
+        <v>-3.381752911825696</v>
       </c>
       <c r="G10">
-        <v>-5.654930981935594</v>
+        <v>-4.493656123340858</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.7050570754663154</v>
       </c>
       <c r="E11">
-        <v>-12.6751135659806</v>
+        <v>-15.62239845053193</v>
       </c>
       <c r="F11">
-        <v>-2.254661312963439</v>
+        <v>-3.211097629705359</v>
       </c>
       <c r="G11">
-        <v>-4.987969282733066</v>
+        <v>-3.883801851324341</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.5959929067527621</v>
       </c>
       <c r="E12">
-        <v>-14.09272918748433</v>
+        <v>-15.8665823571639</v>
       </c>
       <c r="F12">
-        <v>-1.994238340503927</v>
+        <v>-3.503377127374331</v>
       </c>
       <c r="G12">
-        <v>-4.109093445069871</v>
+        <v>-3.219223761933499</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.5042541649172173</v>
       </c>
       <c r="E13">
-        <v>-14.43910701197503</v>
+        <v>-17.55561033874517</v>
       </c>
       <c r="F13">
-        <v>-2.461937889594139</v>
+        <v>-3.482421088818309</v>
       </c>
       <c r="G13">
-        <v>-4.237816207134712</v>
+        <v>-2.696876427121917</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.4356292656182287</v>
       </c>
       <c r="E14">
-        <v>-15.45098295952228</v>
+        <v>-18.17638668225597</v>
       </c>
       <c r="F14">
-        <v>-1.961599836466224</v>
+        <v>-3.262748822372116</v>
       </c>
       <c r="G14">
-        <v>-3.157017550561043</v>
+        <v>-1.657471126040349</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.3920112694693088</v>
       </c>
       <c r="E15">
-        <v>-15.48727787328995</v>
+        <v>-19.50437600336989</v>
       </c>
       <c r="F15">
-        <v>-1.586926775077799</v>
+        <v>-3.321209195089886</v>
       </c>
       <c r="G15">
-        <v>-3.117699737018877</v>
+        <v>-1.088918833455244</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.3675422188323292</v>
       </c>
       <c r="E16">
-        <v>-18.12366581769859</v>
+        <v>-20.56692528229138</v>
       </c>
       <c r="F16">
-        <v>-0.8589492178235655</v>
+        <v>-3.128773648847741</v>
       </c>
       <c r="G16">
-        <v>-2.12304259822899</v>
+        <v>-1.170687354048913</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.3497170932567942</v>
       </c>
       <c r="E17">
-        <v>-18.77438266165008</v>
+        <v>-20.89088822526198</v>
       </c>
       <c r="F17">
-        <v>-1.39206079887584</v>
+        <v>-3.122810231914988</v>
       </c>
       <c r="G17">
-        <v>-1.508099985004394</v>
+        <v>0.4072310123524105</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.317582615177826</v>
       </c>
       <c r="E18">
-        <v>-18.89402422028441</v>
+        <v>-21.60215058390681</v>
       </c>
       <c r="F18">
-        <v>-1.468570468933208</v>
+        <v>-2.949334358788118</v>
       </c>
       <c r="G18">
-        <v>-0.7929491621390958</v>
+        <v>-0.2265690090537973</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.2521890347304792</v>
       </c>
       <c r="E19">
-        <v>-19.51723849884289</v>
+        <v>-22.95631759600113</v>
       </c>
       <c r="F19">
-        <v>-1.139624116546719</v>
+        <v>-2.826042639657648</v>
       </c>
       <c r="G19">
-        <v>-1.195082151508275</v>
+        <v>0.4047116438219863</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.1403318616651593</v>
       </c>
       <c r="E20">
-        <v>-21.7139550327712</v>
+        <v>-23.19827538136299</v>
       </c>
       <c r="F20">
-        <v>-1.086633453789635</v>
+        <v>-2.623739580913355</v>
       </c>
       <c r="G20">
-        <v>-0.9262485594721579</v>
+        <v>0.9128956892267784</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.02191703013428293</v>
       </c>
       <c r="E21">
-        <v>-21.35403358615023</v>
+        <v>-24.20081490985203</v>
       </c>
       <c r="F21">
-        <v>-0.7081383052046931</v>
+        <v>-2.126332291656545</v>
       </c>
       <c r="G21">
-        <v>-0.7685517539351421</v>
+        <v>1.307723815230023</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.2241547758541932</v>
       </c>
       <c r="E22">
-        <v>-21.42333407031632</v>
+        <v>-24.95984335194372</v>
       </c>
       <c r="F22">
-        <v>-1.007004980460727</v>
+        <v>-2.441661940675816</v>
       </c>
       <c r="G22">
-        <v>-1.227873103572658</v>
+        <v>1.026953898923336</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.4460031398925534</v>
       </c>
       <c r="E23">
-        <v>-20.96041298283961</v>
+        <v>-24.58528598861406</v>
       </c>
       <c r="F23">
-        <v>-0.5625303682428044</v>
+        <v>-2.100213867446276</v>
       </c>
       <c r="G23">
-        <v>0.1216964871669416</v>
+        <v>0.8607956701665217</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.6614770860197711</v>
       </c>
       <c r="E24">
-        <v>-21.92282003029683</v>
+        <v>-25.0063759316271</v>
       </c>
       <c r="F24">
-        <v>-0.08929152633007206</v>
+        <v>-1.721037800856233</v>
       </c>
       <c r="G24">
-        <v>0.1073191167036808</v>
+        <v>0.6873769607018217</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.8463759105177641</v>
       </c>
       <c r="E25">
-        <v>-23.2799565884884</v>
+        <v>-25.28479475920963</v>
       </c>
       <c r="F25">
-        <v>-0.3993734678526082</v>
+        <v>-1.793694734123181</v>
       </c>
       <c r="G25">
-        <v>-0.460865060894077</v>
+        <v>0.8618660754488782</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.9840902225122246</v>
       </c>
       <c r="E26">
-        <v>-22.1976172576041</v>
+        <v>-24.78985241241849</v>
       </c>
       <c r="F26">
-        <v>0.07925887421975174</v>
+        <v>-1.609143588820882</v>
       </c>
       <c r="G26">
-        <v>-0.3681653526974175</v>
+        <v>1.27387812235083</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.065739031534437</v>
       </c>
       <c r="E27">
-        <v>-22.39517721390355</v>
+        <v>-25.25147354475053</v>
       </c>
       <c r="F27">
-        <v>0.4534108925118157</v>
+        <v>-1.576983052774594</v>
       </c>
       <c r="G27">
-        <v>-0.8334339785134895</v>
+        <v>0.4261354139366619</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.09115499326607</v>
       </c>
       <c r="E28">
-        <v>-22.12792637157348</v>
+        <v>-24.77639600772605</v>
       </c>
       <c r="F28">
-        <v>-0.1184666262566706</v>
+        <v>-1.775522010040565</v>
       </c>
       <c r="G28">
-        <v>0.4298974968924561</v>
+        <v>0.6594028324080429</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.067775474338871</v>
       </c>
       <c r="E29">
-        <v>-21.68543077739228</v>
+        <v>-24.92291299684335</v>
       </c>
       <c r="F29">
-        <v>-0.4521495834523675</v>
+        <v>-1.821393683337991</v>
       </c>
       <c r="G29">
-        <v>-0.8992612926338199</v>
+        <v>0.6951073754361081</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.007545714230663</v>
       </c>
       <c r="E30">
-        <v>-21.54152615819829</v>
+        <v>-23.74703504050127</v>
       </c>
       <c r="F30">
-        <v>-0.3087293648012723</v>
+        <v>-1.742470150668865</v>
       </c>
       <c r="G30">
-        <v>-0.7419091053828311</v>
+        <v>0.912814756144454</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.9251804534727855</v>
       </c>
       <c r="E31">
-        <v>-21.22944555282803</v>
+        <v>-24.73705679005727</v>
       </c>
       <c r="F31">
-        <v>-0.03646239521653359</v>
+        <v>-1.603788193561783</v>
       </c>
       <c r="G31">
-        <v>-0.920512753605482</v>
+        <v>0.8491491385455653</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.8343797336189586</v>
       </c>
       <c r="E32">
-        <v>-21.50326677547397</v>
+        <v>-23.68526432846709</v>
       </c>
       <c r="F32">
-        <v>-0.05632001859644334</v>
+        <v>-1.597106582090802</v>
       </c>
       <c r="G32">
-        <v>-1.309793047352611</v>
+        <v>-0.1475626562375271</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.7462393659503903</v>
       </c>
       <c r="E33">
-        <v>-20.98823534550463</v>
+        <v>-23.15954253254764</v>
       </c>
       <c r="F33">
-        <v>0.3695867382877281</v>
+        <v>-1.50982482232743</v>
       </c>
       <c r="G33">
-        <v>-1.133411142776997</v>
+        <v>0.1241531978271792</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.6665436528664016</v>
       </c>
       <c r="E34">
-        <v>-20.00172721272943</v>
+        <v>-23.45464896323334</v>
       </c>
       <c r="F34">
-        <v>-0.2551629866992423</v>
+        <v>-1.330391330839626</v>
       </c>
       <c r="G34">
-        <v>-0.8412609907976472</v>
+        <v>0.266663302077689</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.5964704400051525</v>
       </c>
       <c r="E35">
-        <v>-20.0830678565262</v>
+        <v>-22.70799709088963</v>
       </c>
       <c r="F35">
-        <v>0.2444013712744584</v>
+        <v>-1.374401662582961</v>
       </c>
       <c r="G35">
-        <v>-1.503920182914021</v>
+        <v>-0.03463228820433081</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.5321406337918725</v>
       </c>
       <c r="E36">
-        <v>-19.0414922947951</v>
+        <v>-20.52442547080441</v>
       </c>
       <c r="F36">
-        <v>-0.1137996043092982</v>
+        <v>-1.246235001287016</v>
       </c>
       <c r="G36">
-        <v>-1.776891805127053</v>
+        <v>-0.6818645905318166</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.463460644228557</v>
       </c>
       <c r="E37">
-        <v>-17.7408726363118</v>
+        <v>-20.88703819836386</v>
       </c>
       <c r="F37">
-        <v>0.454219379096948</v>
+        <v>-1.49140524475878</v>
       </c>
       <c r="G37">
-        <v>-0.9049239976519446</v>
+        <v>-0.5944307541754327</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3796780152655523</v>
       </c>
       <c r="E38">
-        <v>-18.16391043543618</v>
+        <v>-20.31007823433</v>
       </c>
       <c r="F38">
-        <v>-0.2227605673713368</v>
+        <v>-1.407422872360757</v>
       </c>
       <c r="G38">
-        <v>-2.109584209861801</v>
+        <v>-0.3724313093592966</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.2666747772755255</v>
       </c>
       <c r="E39">
-        <v>-17.39918378740683</v>
+        <v>-19.42990061789306</v>
       </c>
       <c r="F39">
-        <v>0.003604079322072897</v>
+        <v>-0.9598915844265049</v>
       </c>
       <c r="G39">
-        <v>-2.248930091667882</v>
+        <v>-0.6834336480310756</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.1133962783311636</v>
       </c>
       <c r="E40">
-        <v>-16.7372698857236</v>
+        <v>-18.63768386410467</v>
       </c>
       <c r="F40">
-        <v>-0.2095315399486287</v>
+        <v>-1.128556299677915</v>
       </c>
       <c r="G40">
-        <v>-1.766313068043862</v>
+        <v>-1.031458955749432</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.08601988522092394</v>
       </c>
       <c r="E41">
-        <v>-14.29075845666348</v>
+        <v>-17.39867294241387</v>
       </c>
       <c r="F41">
-        <v>0.5204912564231168</v>
+        <v>-0.9014759435484865</v>
       </c>
       <c r="G41">
-        <v>-2.127765435194314</v>
+        <v>-0.6641454669919307</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.3380402480300013</v>
       </c>
       <c r="E42">
-        <v>-16.04467621198387</v>
+        <v>-17.01236199103494</v>
       </c>
       <c r="F42">
-        <v>0.2408244808291701</v>
+        <v>-0.8035115577586114</v>
       </c>
       <c r="G42">
-        <v>-1.345218240709427</v>
+        <v>-1.327546110572181</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.6412315468080216</v>
       </c>
       <c r="E43">
-        <v>-15.07807442108857</v>
+        <v>-16.38855380325702</v>
       </c>
       <c r="F43">
-        <v>0.1125816097321675</v>
+        <v>-1.057806268172212</v>
       </c>
       <c r="G43">
-        <v>-2.614165427730857</v>
+        <v>-1.076319380058532</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.9938838819446731</v>
       </c>
       <c r="E44">
-        <v>-13.58229536245157</v>
+        <v>-15.36568015212162</v>
       </c>
       <c r="F44">
-        <v>-0.1772061587891836</v>
+        <v>-0.8498744529258969</v>
       </c>
       <c r="G44">
-        <v>-1.801223944716229</v>
+        <v>-1.633105046771489</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.394620613949058</v>
       </c>
       <c r="E45">
-        <v>-11.90921986556897</v>
+        <v>-14.60359079328354</v>
       </c>
       <c r="F45">
-        <v>0.05472594521844159</v>
+        <v>-0.7169877541688002</v>
       </c>
       <c r="G45">
-        <v>-2.722239810824583</v>
+        <v>-1.591899664889948</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.836630516210835</v>
       </c>
       <c r="E46">
-        <v>-13.35042572739772</v>
+        <v>-14.14147127559252</v>
       </c>
       <c r="F46">
-        <v>0.2902216857929102</v>
+        <v>-0.6724306999396177</v>
       </c>
       <c r="G46">
-        <v>-2.736990517764373</v>
+        <v>-2.063141674330487</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.321314708875113</v>
       </c>
       <c r="E47">
-        <v>-11.91248844288161</v>
+        <v>-12.85287931710591</v>
       </c>
       <c r="F47">
-        <v>-0.05228835444701815</v>
+        <v>-0.6967209172919075</v>
       </c>
       <c r="G47">
-        <v>-2.78013307213252</v>
+        <v>-2.4815108843118</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.84577318986653</v>
       </c>
       <c r="E48">
-        <v>-11.09033118865253</v>
+        <v>-12.74919439638157</v>
       </c>
       <c r="F48">
-        <v>0.1893389616429725</v>
+        <v>-0.4922086026843488</v>
       </c>
       <c r="G48">
-        <v>-2.820784976160745</v>
+        <v>-2.627072948989321</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.404741371226367</v>
       </c>
       <c r="E49">
-        <v>-10.83333877829479</v>
+        <v>-11.49696795625516</v>
       </c>
       <c r="F49">
-        <v>0.1951814369349174</v>
+        <v>-0.6828060016596814</v>
       </c>
       <c r="G49">
-        <v>-3.204768069132505</v>
+        <v>-2.832003345668759</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.999590161347072</v>
       </c>
       <c r="E50">
-        <v>-9.945623083303284</v>
+        <v>-11.1006976041193</v>
       </c>
       <c r="F50">
-        <v>-0.02195105505429185</v>
+        <v>-0.2620243538966306</v>
       </c>
       <c r="G50">
-        <v>-3.204525269885531</v>
+        <v>-3.061250217469825</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.622500779349432</v>
       </c>
       <c r="E51">
-        <v>-8.980379392511207</v>
+        <v>-10.34709325601783</v>
       </c>
       <c r="F51">
-        <v>0.1456657754325769</v>
+        <v>-0.3060727905404943</v>
       </c>
       <c r="G51">
-        <v>-2.852868416440936</v>
+        <v>-3.369234535394277</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.271741961696136</v>
       </c>
       <c r="E52">
-        <v>-10.07491670505652</v>
+        <v>-9.346406059779671</v>
       </c>
       <c r="F52">
-        <v>0.2820597817731267</v>
+        <v>-0.1987362559553456</v>
       </c>
       <c r="G52">
-        <v>-3.322781556884598</v>
+        <v>-3.47950716543372</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.946326865900461</v>
       </c>
       <c r="E53">
-        <v>-8.147211975060003</v>
+        <v>-9.250346435047712</v>
       </c>
       <c r="F53">
-        <v>0.4459746383368845</v>
+        <v>-0.02339489943737139</v>
       </c>
       <c r="G53">
-        <v>-3.600444687127861</v>
+        <v>-3.92115638493399</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.637461210278184</v>
       </c>
       <c r="E54">
-        <v>-7.733718255560073</v>
+        <v>-8.249119321337322</v>
       </c>
       <c r="F54">
-        <v>0.4197410710576269</v>
+        <v>-0.150084581654125</v>
       </c>
       <c r="G54">
-        <v>-3.528638767893881</v>
+        <v>-4.334116132122516</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.348244541748092</v>
       </c>
       <c r="E55">
-        <v>-6.828633830808138</v>
+        <v>-7.677425629263347</v>
       </c>
       <c r="F55">
-        <v>0.1559830914344447</v>
+        <v>-0.06775231712247931</v>
       </c>
       <c r="G55">
-        <v>-3.976467619841316</v>
+        <v>-4.593198593110825</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.071493039544631</v>
       </c>
       <c r="E56">
-        <v>-6.477076951795376</v>
+        <v>-7.127390934248354</v>
       </c>
       <c r="F56">
-        <v>-0.3968833954397929</v>
+        <v>0.2679576551078679</v>
       </c>
       <c r="G56">
-        <v>-4.208972700892092</v>
+        <v>-4.722378235479111</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.799532720149932</v>
       </c>
       <c r="E57">
-        <v>-7.05216797073306</v>
+        <v>-6.523484935139011</v>
       </c>
       <c r="F57">
-        <v>0.4082367045675474</v>
+        <v>0.01244110277513802</v>
       </c>
       <c r="G57">
-        <v>-4.64017894202791</v>
+        <v>-4.84091909363861</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.531950526514368</v>
       </c>
       <c r="E58">
-        <v>-6.039228801086653</v>
+        <v>-5.072315519341995</v>
       </c>
       <c r="F58">
-        <v>0.3502998600483472</v>
+        <v>0.1359440555933219</v>
       </c>
       <c r="G58">
-        <v>-5.139528227736374</v>
+        <v>-5.40662306387481</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.25684612253928</v>
       </c>
       <c r="E59">
-        <v>-6.607911414950125</v>
+        <v>-5.257100197606266</v>
       </c>
       <c r="F59">
-        <v>0.02039508657681888</v>
+        <v>0.4309174040561979</v>
       </c>
       <c r="G59">
-        <v>-5.152621111860807</v>
+        <v>-5.172867436164891</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.9706853208847</v>
       </c>
       <c r="E60">
-        <v>-4.299124626632639</v>
+        <v>-5.393724237347826</v>
       </c>
       <c r="F60">
-        <v>0.4654826906728128</v>
+        <v>0.1555846467136982</v>
       </c>
       <c r="G60">
-        <v>-5.26490923672459</v>
+        <v>-5.407338407892775</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.66517964920376</v>
       </c>
       <c r="E61">
-        <v>-5.278339720321439</v>
+        <v>-4.062362508638139</v>
       </c>
       <c r="F61">
-        <v>0.09503264630385994</v>
+        <v>0.009434129102975817</v>
       </c>
       <c r="G61">
-        <v>-5.4081242420147</v>
+        <v>-6.071725912928466</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-12.32522335453872</v>
       </c>
       <c r="E62">
-        <v>-3.741576772331032</v>
+        <v>-4.750524705894279</v>
       </c>
       <c r="F62">
-        <v>0.4200169174027591</v>
+        <v>-0.3536111390523523</v>
       </c>
       <c r="G62">
-        <v>-5.259426673083252</v>
+        <v>-6.3421703343773</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.94710212531398</v>
       </c>
       <c r="E63">
-        <v>-4.659868409095922</v>
+        <v>-3.213537484492331</v>
       </c>
       <c r="F63">
-        <v>-0.2593570108596162</v>
+        <v>-0.02255079305391869</v>
       </c>
       <c r="G63">
-        <v>-5.188356983823966</v>
+        <v>-6.167707327076155</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-13.51438573679217</v>
       </c>
       <c r="E64">
-        <v>-3.095677653516347</v>
+        <v>-2.846821384143945</v>
       </c>
       <c r="F64">
-        <v>0.08346283878895923</v>
+        <v>-0.2353078484215409</v>
       </c>
       <c r="G64">
-        <v>-5.558620613969425</v>
+        <v>-6.023795252980217</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-14.0145123111514</v>
       </c>
       <c r="E65">
-        <v>-3.469229939705401</v>
+        <v>-2.53568771095574</v>
       </c>
       <c r="F65">
-        <v>0.06484859488065155</v>
+        <v>0.05535136260755522</v>
       </c>
       <c r="G65">
-        <v>-5.688332848234298</v>
+        <v>-6.24613931608238</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-14.43704858750069</v>
       </c>
       <c r="E66">
-        <v>-2.696603883736222</v>
+        <v>-3.037009390341819</v>
       </c>
       <c r="F66">
-        <v>0.2438380814405547</v>
+        <v>-0.2653726149387462</v>
       </c>
       <c r="G66">
-        <v>-5.70165808862734</v>
+        <v>-6.055306940194955</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-14.76628112570279</v>
       </c>
       <c r="E67">
-        <v>-3.65128595812926</v>
+        <v>-3.294790910851277</v>
       </c>
       <c r="F67">
-        <v>0.4375054100106623</v>
+        <v>-0.4058413605336668</v>
       </c>
       <c r="G67">
-        <v>-6.297751125904099</v>
+        <v>-6.239628119072144</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-14.99568399521495</v>
       </c>
       <c r="E68">
-        <v>-4.050974403185459</v>
+        <v>-3.589153916709825</v>
       </c>
       <c r="F68">
-        <v>-0.2147709637713356</v>
+        <v>-0.4339495232454595</v>
       </c>
       <c r="G68">
-        <v>-5.310487615796245</v>
+        <v>-5.727225110408113</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-15.11319093795659</v>
       </c>
       <c r="E69">
-        <v>-2.948172200103736</v>
+        <v>-3.158150258264418</v>
       </c>
       <c r="F69">
-        <v>0.09637128802678394</v>
+        <v>-0.5509357097058197</v>
       </c>
       <c r="G69">
-        <v>-6.002995450822818</v>
+        <v>-5.70367619419627</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-15.11304568969328</v>
       </c>
       <c r="E70">
-        <v>-3.603872897645017</v>
+        <v>-2.611691478200102</v>
       </c>
       <c r="F70">
-        <v>-0.2767113079482658</v>
+        <v>-0.5235830180653801</v>
       </c>
       <c r="G70">
-        <v>-6.017785318931474</v>
+        <v>-5.618505873400382</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-15.00007204749254</v>
       </c>
       <c r="E71">
-        <v>-3.209483950239298</v>
+        <v>-2.768898833267512</v>
       </c>
       <c r="F71">
-        <v>-0.5666746903590103</v>
+        <v>-0.3846550358396666</v>
       </c>
       <c r="G71">
-        <v>-5.180885032804199</v>
+        <v>-5.026347228222431</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-14.77621532038085</v>
       </c>
       <c r="E72">
-        <v>-3.44392442310322</v>
+        <v>-3.831597627796691</v>
       </c>
       <c r="F72">
-        <v>-0.6004099528380202</v>
+        <v>-0.5744124702685606</v>
       </c>
       <c r="G72">
-        <v>-4.703625257081145</v>
+        <v>-5.433939284531628</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-14.45529100917528</v>
       </c>
       <c r="E73">
-        <v>-3.282563856710981</v>
+        <v>-3.547941600733551</v>
       </c>
       <c r="F73">
-        <v>-0.8059129948593272</v>
+        <v>-0.764671895343551</v>
       </c>
       <c r="G73">
-        <v>-4.460173323959831</v>
+        <v>-5.09702530579305</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-14.04708228569978</v>
       </c>
       <c r="E74">
-        <v>-5.033021986997792</v>
+        <v>-3.411982074803964</v>
       </c>
       <c r="F74">
-        <v>-0.9533193174526936</v>
+        <v>-0.6746076494741747</v>
       </c>
       <c r="G74">
-        <v>-4.659822184331445</v>
+        <v>-4.797619894594995</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-13.5659452302623</v>
       </c>
       <c r="E75">
-        <v>-4.543798612200939</v>
+        <v>-3.751536173087971</v>
       </c>
       <c r="F75">
-        <v>-0.4861954837074272</v>
+        <v>-0.7730276373355895</v>
       </c>
       <c r="G75">
-        <v>-3.871312049200455</v>
+        <v>-4.739737076265423</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-13.02920439290575</v>
       </c>
       <c r="E76">
-        <v>-5.679701909541545</v>
+        <v>-4.475374455624388</v>
       </c>
       <c r="F76">
-        <v>-0.4755095442113136</v>
+        <v>-0.5484779436217136</v>
       </c>
       <c r="G76">
-        <v>-4.725250054529336</v>
+        <v>-4.361487178415748</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-12.44346337790341</v>
       </c>
       <c r="E77">
-        <v>-5.124010540702136</v>
+        <v>-4.26436640105515</v>
       </c>
       <c r="F77">
-        <v>-0.5901497941869456</v>
+        <v>-0.9973685824639601</v>
       </c>
       <c r="G77">
-        <v>-4.076456526936364</v>
+        <v>-4.017184792484319</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.82427721604593</v>
       </c>
       <c r="E78">
-        <v>-5.739786417777839</v>
+        <v>-5.359036616362858</v>
       </c>
       <c r="F78">
-        <v>-0.6143240401028435</v>
+        <v>-1.040143818409721</v>
       </c>
       <c r="G78">
-        <v>-3.772041096867964</v>
+        <v>-3.28500669339578</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-11.18157687530628</v>
       </c>
       <c r="E79">
-        <v>-5.406507821805648</v>
+        <v>-4.902415950465909</v>
       </c>
       <c r="F79">
-        <v>-0.9882109808260116</v>
+        <v>-0.715013754647929</v>
       </c>
       <c r="G79">
-        <v>-3.294256561482095</v>
+        <v>-2.930146456337889</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.52013957370278</v>
       </c>
       <c r="E80">
-        <v>-7.831351947384142</v>
+        <v>-5.450108234293698</v>
       </c>
       <c r="F80">
-        <v>-0.1498700344967999</v>
+        <v>-0.8875187811787176</v>
       </c>
       <c r="G80">
-        <v>-3.062994194856689</v>
+        <v>-2.749135701602232</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.849203103484189</v>
       </c>
       <c r="E81">
-        <v>-7.683427019627724</v>
+        <v>-7.506388080484258</v>
       </c>
       <c r="F81">
-        <v>-0.9284169365897349</v>
+        <v>-0.8686618256213897</v>
       </c>
       <c r="G81">
-        <v>-2.242468498804877</v>
+        <v>-1.876288073199918</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.162747054373931</v>
       </c>
       <c r="E82">
-        <v>-9.569354596907791</v>
+        <v>-7.343852155287093</v>
       </c>
       <c r="F82">
-        <v>-0.8988243394921254</v>
+        <v>-0.9970761687707719</v>
       </c>
       <c r="G82">
-        <v>-2.188963899154601</v>
+        <v>-1.85481208819342</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.463113483722909</v>
       </c>
       <c r="E83">
-        <v>-8.302890948359876</v>
+        <v>-8.284479762556911</v>
       </c>
       <c r="F83">
-        <v>-1.230664179216593</v>
+        <v>-1.056859444230812</v>
       </c>
       <c r="G83">
-        <v>-2.024954313196273</v>
+        <v>-1.219001793452055</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.751985154085686</v>
       </c>
       <c r="E84">
-        <v>-10.06979579549301</v>
+        <v>-10.18197403337663</v>
       </c>
       <c r="F84">
-        <v>-1.088848508224721</v>
+        <v>-1.012429958581661</v>
       </c>
       <c r="G84">
-        <v>-1.898236602977408</v>
+        <v>-0.8800958165904572</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.02892408952698</v>
       </c>
       <c r="E85">
-        <v>-12.3027740174984</v>
+        <v>-10.58171231696872</v>
       </c>
       <c r="F85">
-        <v>-0.9723800513911102</v>
+        <v>-1.28388926994867</v>
       </c>
       <c r="G85">
-        <v>-1.429926459712689</v>
+        <v>-0.5663913572668759</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.310437732796618</v>
       </c>
       <c r="E86">
-        <v>-12.47240778084969</v>
+        <v>-11.59756704096516</v>
       </c>
       <c r="F86">
-        <v>-1.094468152685313</v>
+        <v>-1.064355340858745</v>
       </c>
       <c r="G86">
-        <v>-1.356969202114028</v>
+        <v>-0.02377159070529954</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.611759258602301</v>
       </c>
       <c r="E87">
-        <v>-14.63159174403553</v>
+        <v>-12.85504314020615</v>
       </c>
       <c r="F87">
-        <v>-1.262171133382072</v>
+        <v>-1.562908262233627</v>
       </c>
       <c r="G87">
-        <v>-1.661496894199846</v>
+        <v>-0.3452195184861229</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.95186972427473</v>
       </c>
       <c r="E88">
-        <v>-15.67750741160108</v>
+        <v>-13.32444739056092</v>
       </c>
       <c r="F88">
-        <v>-1.320382995879002</v>
+        <v>-1.542104643279721</v>
       </c>
       <c r="G88">
-        <v>-0.9159178431251227</v>
+        <v>0.2725113699617828</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.355225730019018</v>
       </c>
       <c r="E89">
-        <v>-17.68720068636103</v>
+        <v>-15.06314777958714</v>
       </c>
       <c r="F89">
-        <v>-1.546835449517109</v>
+        <v>-1.798348502192108</v>
       </c>
       <c r="G89">
-        <v>-1.112935072948896</v>
+        <v>0.3349394946244837</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.836798902262526</v>
       </c>
       <c r="E90">
-        <v>-18.9379984217917</v>
+        <v>-17.45814692858542</v>
       </c>
       <c r="F90">
-        <v>-1.359743701390423</v>
+        <v>-1.633985498863436</v>
       </c>
       <c r="G90">
-        <v>-0.1468864733884288</v>
+        <v>0.9903329845437896</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.417459607590694</v>
       </c>
       <c r="E91">
-        <v>-21.01910201207076</v>
+        <v>-18.97815582209147</v>
       </c>
       <c r="F91">
-        <v>-1.60567521450536</v>
+        <v>-1.911983942508145</v>
       </c>
       <c r="G91">
-        <v>-0.2819115728962168</v>
+        <v>1.12245493606626</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.115025281844818</v>
       </c>
       <c r="E92">
-        <v>-21.54129773157543</v>
+        <v>-20.72578146225474</v>
       </c>
       <c r="F92">
-        <v>-1.242966263515569</v>
+        <v>-2.193109473098421</v>
       </c>
       <c r="G92">
-        <v>-0.5076757114127382</v>
+        <v>0.6685195525202104</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.938887125196439</v>
       </c>
       <c r="E93">
-        <v>-22.17298040802522</v>
+        <v>-22.21842069313017</v>
       </c>
       <c r="F93">
-        <v>-1.375809058800317</v>
+        <v>-2.466506335820578</v>
       </c>
       <c r="G93">
-        <v>-0.5390124787398709</v>
+        <v>0.989834332326887</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.897254228977172</v>
       </c>
       <c r="E94">
-        <v>-26.19314776127421</v>
+        <v>-24.45692683940891</v>
       </c>
       <c r="F94">
-        <v>-1.989915091028716</v>
+        <v>-2.355153876066658</v>
       </c>
       <c r="G94">
-        <v>-0.8857663538423554</v>
+        <v>0.7281359052582823</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.990515586057916</v>
       </c>
       <c r="E95">
-        <v>-27.39732569958367</v>
+        <v>-26.9931767055646</v>
       </c>
       <c r="F95">
-        <v>-1.915269247627647</v>
+        <v>-2.587549037452448</v>
       </c>
       <c r="G95">
-        <v>-0.66193938781244</v>
+        <v>0.1681050830185714</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.210165122149441</v>
       </c>
       <c r="E96">
-        <v>-30.97256575342076</v>
+        <v>-29.4476789132137</v>
       </c>
       <c r="F96">
-        <v>-2.474539842892928</v>
+        <v>-2.833489662608816</v>
       </c>
       <c r="G96">
-        <v>-0.7464648546943238</v>
+        <v>0.5017843492087605</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.538118258644115</v>
       </c>
       <c r="E97">
-        <v>-32.02031921699754</v>
+        <v>-31.61190072173655</v>
       </c>
       <c r="F97">
-        <v>-2.096955070083663</v>
+        <v>-2.973601381853129</v>
       </c>
       <c r="G97">
-        <v>-1.169656109935423</v>
+        <v>-0.2939967096084802</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.950502356741845</v>
       </c>
       <c r="E98">
-        <v>-34.65103387473646</v>
+        <v>-33.11599243284019</v>
       </c>
       <c r="F98">
-        <v>-2.880409220670782</v>
+        <v>-3.384882483873473</v>
       </c>
       <c r="G98">
-        <v>-1.506058382734143</v>
+        <v>-0.3850150982884626</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.404352538247552</v>
       </c>
       <c r="E99">
-        <v>-39.20817407338385</v>
+        <v>-36.19941335480242</v>
       </c>
       <c r="F99">
-        <v>-2.345801608089051</v>
+        <v>-3.46246903155448</v>
       </c>
       <c r="G99">
-        <v>-2.572926106169632</v>
+        <v>-0.6880833841478484</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.870784392492475</v>
       </c>
       <c r="E100">
-        <v>-40.33004366965786</v>
+        <v>-38.64574411916991</v>
       </c>
       <c r="F100">
-        <v>-2.945484935467308</v>
+        <v>-3.89307428834733</v>
       </c>
       <c r="G100">
-        <v>-2.128948102494089</v>
+        <v>-0.9083545160446674</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.286019405024921</v>
       </c>
       <c r="E101">
-        <v>-42.87441514055926</v>
+        <v>-41.06860923955212</v>
       </c>
       <c r="F101">
-        <v>-3.466498210601697</v>
+        <v>-3.828744104213324</v>
       </c>
       <c r="G101">
-        <v>-2.728090489453268</v>
+        <v>-1.448723820768704</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.636466038592803</v>
       </c>
       <c r="E102">
-        <v>-43.73080523913325</v>
+        <v>-43.1722979930156</v>
       </c>
       <c r="F102">
-        <v>-3.016384073105515</v>
+        <v>-4.093463818391156</v>
       </c>
       <c r="G102">
-        <v>-3.571300945257263</v>
+        <v>-1.93585743253535</v>
       </c>
     </row>
   </sheetData>
